--- a/test/fixtures/historic_data-consumption.xlsx
+++ b/test/fixtures/historic_data-consumption.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1da6715471b04c19/Energiepad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EC93BFC-263D-4D1F-863B-4415151813C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AB731EA-8FC4-4059-AA07-192D347B1EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{D3870705-77A9-49FD-9C58-3F5E58A39F36}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="26">
   <si>
     <t xml:space="preserve">Year </t>
   </si>
@@ -61,10 +61,13 @@
     <t>Uses</t>
   </si>
   <si>
-    <t>Heating,Cooling</t>
-  </si>
-  <si>
-    <t>Year</t>
+    <t>Heating;Cooling</t>
+  </si>
+  <si>
+    <t>Site Code</t>
+  </si>
+  <si>
+    <t>Site Name</t>
   </si>
   <si>
     <t xml:space="preserve">Jan </t>
@@ -103,13 +106,16 @@
     <t>Dec</t>
   </si>
   <si>
-    <t>Site</t>
-  </si>
-  <si>
     <t>Site 604</t>
   </si>
   <si>
+    <t>Main Building A</t>
+  </si>
+  <si>
     <t>site 606</t>
+  </si>
+  <si>
+    <t>Main Building B</t>
   </si>
   <si>
     <t>C</t>
@@ -470,16 +476,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2664A647-48E5-4B2E-ABE7-7C038F564FB0}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,7 +493,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -495,7 +501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -503,7 +509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -511,7 +517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -551,107 +557,122 @@
       <c r="M5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>84</v>
+      </c>
+      <c r="E6">
+        <v>68</v>
+      </c>
+      <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6">
+        <v>432</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>648</v>
+      </c>
+      <c r="J6">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>123</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>465</v>
+      </c>
+      <c r="N6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>5132</v>
       </c>
       <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>845</v>
+      </c>
+      <c r="H7">
         <v>49</v>
       </c>
-      <c r="F7">
-        <v>432</v>
-      </c>
-      <c r="G7">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>648</v>
-      </c>
       <c r="I7">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J7">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L7">
-        <v>465</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>451</v>
-      </c>
-      <c r="C8">
-        <v>5132</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>54</v>
-      </c>
-      <c r="F8">
-        <v>845</v>
-      </c>
-      <c r="G8">
-        <v>49</v>
-      </c>
-      <c r="H8">
-        <v>66</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8">
         <v>63</v>
       </c>
-      <c r="M8">
+      <c r="N7">
         <v>2</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="17" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{B9AC30E6-B500-4E92-AD61-EB211F479847}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{8C26E5BE-D3F7-41AD-86B5-63C72B8EC12F}">
+      <formula1>"Heating, Heating;Cooling, Heating;Cooling;Powering;Lighting, Heating;Powering;Lighting, Cooling, Cooling;Powering;Lighting, Powering;Lighting"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3000B5-86EF-43A1-937B-69154E16AC7B}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -659,7 +680,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -667,7 +688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -675,7 +696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -683,7 +704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -723,109 +744,121 @@
       <c r="M5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>84</v>
+      </c>
+      <c r="E6">
+        <v>68</v>
+      </c>
+      <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6">
+        <v>432</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>648</v>
+      </c>
+      <c r="J6">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>123</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>465</v>
+      </c>
+      <c r="N6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>5132</v>
       </c>
       <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>845</v>
+      </c>
+      <c r="H7">
         <v>49</v>
       </c>
-      <c r="F7">
-        <v>432</v>
-      </c>
-      <c r="G7">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>648</v>
-      </c>
       <c r="I7">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J7">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L7">
-        <v>465</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>451</v>
-      </c>
-      <c r="C8">
-        <v>5132</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>54</v>
-      </c>
-      <c r="F8">
-        <v>845</v>
-      </c>
-      <c r="G8">
-        <v>49</v>
-      </c>
-      <c r="H8">
-        <v>66</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8">
         <v>63</v>
       </c>
-      <c r="M8">
+      <c r="N7">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{14B6370E-7B71-4F71-B337-0A9B14B954DB}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{27E39B78-0336-4EF6-9127-FCDB2606DCFB}">
+      <formula1>"Heating, Heating;Cooling, Heating;Cooling;Powering;Lighting, Heating;Powering;Lighting, Cooling, Cooling;Powering;Lighting, Powering;Lighting"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B321743A-CD25-4F45-950F-509F14C84ECE}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
     <col min="3" max="3" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -833,7 +866,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -841,7 +874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -849,7 +882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -857,7 +890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -897,111 +930,126 @@
       <c r="M5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>84</v>
+      </c>
+      <c r="E6">
+        <v>68</v>
+      </c>
+      <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6">
+        <v>432</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>648</v>
+      </c>
+      <c r="J6">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>123</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>465</v>
+      </c>
+      <c r="N6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>5132</v>
       </c>
       <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>845</v>
+      </c>
+      <c r="H7">
         <v>49</v>
       </c>
-      <c r="F7">
-        <v>432</v>
-      </c>
-      <c r="G7">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>648</v>
-      </c>
       <c r="I7">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J7">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L7">
-        <v>465</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>451</v>
-      </c>
-      <c r="C8">
-        <v>5132</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>54</v>
-      </c>
-      <c r="F8">
-        <v>845</v>
-      </c>
-      <c r="G8">
-        <v>49</v>
-      </c>
-      <c r="H8">
-        <v>66</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8">
         <v>63</v>
       </c>
-      <c r="M8">
+      <c r="N7">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="5:5">
-      <c r="E28" t="s">
-        <v>23</v>
+    <row r="27" spans="5:5">
+      <c r="E27" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{094F5D0D-87B6-4B3C-93A2-0447A7E79493}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{21780EEC-9FFC-4CB0-B04C-18AD5B1FB1DA}">
+      <formula1>"Heating, Heating;Cooling, Heating;Cooling;Powering;Lighting, Heating;Powering;Lighting, Cooling, Cooling;Powering;Lighting, Powering;Lighting"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207CD85C-1F1D-4C7A-95EB-6A1A94444757}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1009,7 +1057,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1017,7 +1065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1025,7 +1073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1033,7 +1081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1073,109 +1121,122 @@
       <c r="M5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>84</v>
+      </c>
+      <c r="E6">
+        <v>68</v>
+      </c>
+      <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6">
+        <v>432</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>648</v>
+      </c>
+      <c r="J6">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>123</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>465</v>
+      </c>
+      <c r="N6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>5132</v>
       </c>
       <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>845</v>
+      </c>
+      <c r="H7">
         <v>49</v>
       </c>
-      <c r="F7">
-        <v>432</v>
-      </c>
-      <c r="G7">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>648</v>
-      </c>
       <c r="I7">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J7">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L7">
-        <v>465</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>451</v>
-      </c>
-      <c r="C8">
-        <v>5132</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>54</v>
-      </c>
-      <c r="F8">
-        <v>845</v>
-      </c>
-      <c r="G8">
-        <v>49</v>
-      </c>
-      <c r="H8">
-        <v>66</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8">
         <v>63</v>
       </c>
-      <c r="M8">
+      <c r="N7">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{19828C88-0D83-4A5E-A2C7-5437B09D8B0C}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{0D816260-E561-4503-BCF1-9D65B3464E59}">
+      <formula1>"Heating, Heating;Cooling, Heating;Cooling;Powering;Lighting, Heating;Powering;Lighting, Cooling, Cooling;Powering;Lighting, Powering;Lighting"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D50EB51E-CCE3-4A25-82FA-19599884D849}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1183,7 +1244,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1191,7 +1252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1207,7 +1268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1247,106 +1308,121 @@
       <c r="M5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>84</v>
+      </c>
+      <c r="E6">
+        <v>68</v>
+      </c>
+      <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6">
+        <v>432</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>648</v>
+      </c>
+      <c r="J6">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>123</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>465</v>
+      </c>
+      <c r="N6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>5132</v>
       </c>
       <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>845</v>
+      </c>
+      <c r="H7">
         <v>49</v>
       </c>
-      <c r="F7">
-        <v>432</v>
-      </c>
-      <c r="G7">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>648</v>
-      </c>
       <c r="I7">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J7">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L7">
-        <v>465</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>451</v>
-      </c>
-      <c r="C8">
-        <v>5132</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>54</v>
-      </c>
-      <c r="F8">
-        <v>845</v>
-      </c>
-      <c r="G8">
-        <v>49</v>
-      </c>
-      <c r="H8">
-        <v>66</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8">
         <v>63</v>
       </c>
-      <c r="M8">
+      <c r="N7">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{B0AACDD5-DDDB-4531-A344-1736AFE51DF6}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{B7F788B8-F0C7-47A0-873D-F845451E9B0F}">
+      <formula1>"Heating, Heating;Cooling, Heating;Cooling;Powering;Lighting, Heating;Powering;Lighting, Cooling, Cooling;Powering;Lighting, Powering;Lighting"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6735630E-2F15-45E9-9534-10F81ADB87FE}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1430,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1362,7 +1438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1370,7 +1446,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1378,7 +1454,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1418,95 +1494,107 @@
       <c r="M5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>84</v>
+      </c>
+      <c r="E6">
+        <v>68</v>
+      </c>
+      <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6">
+        <v>432</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>648</v>
+      </c>
+      <c r="J6">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>123</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>465</v>
+      </c>
+      <c r="N6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>5132</v>
       </c>
       <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>845</v>
+      </c>
+      <c r="H7">
         <v>49</v>
       </c>
-      <c r="F7">
-        <v>432</v>
-      </c>
-      <c r="G7">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>648</v>
-      </c>
       <c r="I7">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J7">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L7">
-        <v>465</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>451</v>
-      </c>
-      <c r="C8">
-        <v>5132</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>54</v>
-      </c>
-      <c r="F8">
-        <v>845</v>
-      </c>
-      <c r="G8">
-        <v>49</v>
-      </c>
-      <c r="H8">
-        <v>66</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8">
         <v>63</v>
       </c>
-      <c r="M8">
+      <c r="N7">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{013C8653-8EB6-4F1A-9AD1-6B0FD4EBCFD8}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{CBD0C89C-373E-42BF-A12E-911683909831}">
+      <formula1>"Heating, Heating;Cooling, Heating;Cooling;Powering;Lighting, Heating;Powering;Lighting, Cooling, Cooling;Powering;Lighting, Powering;Lighting"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>